--- a/output/2026-09-01_09_Italia_Toscana_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-01_09_Italia_Toscana_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,6 @@
           <t>055 8839720</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>Officina meccanica di precisione, tornitura/fresatura CNC.</t>
@@ -544,7 +543,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -574,7 +573,6 @@
           <t>055 8457844</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Costruzioni metalliche inox/ferro/alluminio, taglio laser tubo e lamiera. 75 dipendenti.</t>
@@ -582,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -607,8 +605,6 @@
           <t>Metalworking / Lavorazioni Metalliche</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Tornitura/fresatura CNC, lavorazione metalli e leghe. 90 dipendenti.</t>
@@ -616,7 +612,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -641,8 +637,6 @@
           <t>Metalworking / Lavorazioni Metalliche</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>Meccanica di precisione, fresatura CNC. Attiva dal 1974.</t>
@@ -650,7 +644,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -692,7 +686,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -722,7 +716,6 @@
           <t>0571 501890</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>Carpenteria metallica leggera/pesante, inox, lavorazioni conto terzi.</t>
@@ -730,7 +723,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -760,7 +753,6 @@
           <t>055 8248037</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>Tornitura, fresatura conto terzi, oltre 50 anni.</t>
@@ -768,7 +760,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -810,7 +802,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -835,8 +827,6 @@
           <t>Metalworking / Lavorazioni Metalliche</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>Fabbri/carpenteria in ferro battuto dal 1914. Premiata tra le 100 attività storiche di Firenze.</t>
@@ -844,7 +834,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -869,8 +859,6 @@
           <t>Metalworking / Lavorazioni Metalliche</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>Carpenteria metallica pesante certificata UNI EN 1090-1, dal 1984.</t>
@@ -878,7 +866,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -888,7 +876,6 @@
           <t>Prato Infissi di Paolo Degl'Innocenti</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>Prato (PO)</t>
@@ -899,8 +886,6 @@
           <t>Metalworking / Lavorazioni Metalliche</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>P.IVA 01589860970, Via Roma 523/d. Attività prevalente infissi/serramenti metallici e carpenteria leggera: fit settoriale marginale.</t>
@@ -938,7 +923,6 @@
           <t>0573 518065</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>Meccanica di precisione, tornitura automatica CNC, dal 2009.</t>
@@ -946,7 +930,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -956,7 +940,6 @@
           <t>Metastil Srl</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
           <t>Serravalle Pistoiese (PT)</t>
@@ -972,7 +955,6 @@
           <t>0573 916017</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>Ragione sociale individuata tramite indirizzo (Via G. Zeti) e telefono. Saldatura e lavorazione metalli.</t>
@@ -980,7 +962,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1010,7 +992,6 @@
           <t>0573 775043</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>Carpenteria metallica, prefabbricati metallici, saldatura. P.IVA 00357190479.</t>
@@ -1018,7 +999,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1060,7 +1041,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1051,6 @@
           <t>Metallic di Gretcan Dorin</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
           <t>Pistoia (PT)</t>
@@ -1086,7 +1066,6 @@
           <t>0573 760082</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>Carpenteria metallica, ditta individuale. Via Galvani Luigi 14.</t>
@@ -1094,7 +1073,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1083,6 @@
           <t>O.Me.P. Officine Meccaniche Pierallini S.p.A.</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
           <t>Pistoia (PT)</t>
@@ -1120,7 +1098,6 @@
           <t>0573 92721</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
           <t>Voce unificata (duplicati 'O.Me.P.' e 'Officine Meccaniche Pierallini SpA'). Carpenteria/saldatura per aerospace, automotive, ferroviario. 65 dipendenti.</t>
@@ -1128,7 +1105,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1138,7 +1115,6 @@
           <t>C.B.A. Pistoia Srl</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
           <t>Pistoia (PT)</t>
@@ -1154,7 +1130,6 @@
           <t>0573 31702</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>Carpenteria metallica, prefabbricati metallici.</t>
@@ -1162,7 +1137,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1192,7 +1167,6 @@
           <t>0573 544156</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>Carpenteria dal 1963.</t>
@@ -1200,7 +1174,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1184,6 @@
           <t>M.V. Lavorazione in Ferro di Miedico Valter</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
           <t>Pistoia (PT)</t>
@@ -1226,7 +1199,6 @@
           <t>0573 531784</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>Carpenteria pesante e navale, dal 2004.</t>
@@ -1234,7 +1206,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1236,6 @@
           <t>0573 380259</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>Carpenteria leggera per settore ferroviario e macchinari industriali, certificata UNI EN 1090-1 e ISO 3834-3.</t>
@@ -1272,7 +1243,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1253,6 @@
           <t>Officina Ilias di Hoxha Nertil</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
           <t>Pistoia (PT)</t>
@@ -1293,8 +1263,6 @@
           <t>Metalworking / Lavorazioni Metalliche</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>Ditta individuale, fabbricazione strutture metalliche. Via G.B. Vico 4.</t>
@@ -1302,7 +1270,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1322,6 @@
           <t>Amt Srl</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
           <t>Pistoia (PT)</t>
@@ -1365,8 +1332,6 @@
           <t>Metalworking / Lavorazioni Metalliche</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>Carpenteria metallica, fondata 2019. Via Bure Vecchia Nord 115.</t>
@@ -1374,7 +1339,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1369,6 @@
           <t>0573 382707</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>Carpenteria metallica, saldatura MIG/TIG certificata UNI 3834-2.</t>
@@ -1412,7 +1376,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1418,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1448,6 @@
           <t>0583 980107</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>Carpenteria metallica certificata ISO 9001, dal 2001.</t>
@@ -1492,7 +1455,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1517,8 +1480,6 @@
           <t>Metalworking / Lavorazioni Metalliche</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
           <t>Ragione sociale completa individuata (raw list: 'La Aldo Lambardi'). Costruzioni metalliche dal 1960/1967.</t>
@@ -1526,7 +1487,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1517,6 @@
           <t>050 937751</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
           <t>Carpenteria in ferro, impianti industriali, dal 2000.</t>
@@ -1564,7 +1524,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1534,6 @@
           <t>Gioli Novileno Srl</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
           <t>Vicopisano (PI)</t>
@@ -1590,7 +1549,6 @@
           <t>050 703395</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>Ragione sociale individuata tramite indirizzo (Via Provinciale Vicarese 138) e telefono. Officina meccanica di precisione, carpenteria nautica, oltre 50 anni.</t>
@@ -1598,7 +1556,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1608,7 +1566,6 @@
           <t>Officina Moderna di Papini Simone e Papini Luca Snc</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
           <t>Pisa (PI)</t>
@@ -1624,7 +1581,6 @@
           <t>050 564836</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>Voce unificata: coincide con 'Azienda meccanica (Via Ventiquattro Maggio)' della lista grezza, stesso indirizzo/telefono.</t>
@@ -1674,7 +1630,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1640,6 @@
           <t>Officina Meccanica Or.Ma Srl</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
           <t>Vicopisano (PI)</t>
@@ -1695,8 +1650,6 @@
           <t>Metalworking / Lavorazioni Metalliche</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
           <t>Fabbricazione prodotti in metallo. P.IVA 01154710501.</t>
@@ -1704,7 +1657,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1687,6 @@
           <t>050 741718</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
           <t>Officina meccanica.</t>
@@ -1772,7 +1724,6 @@
           <t>0586 692434</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
           <t>Carpenteria metallica, lavorazione tubi.</t>
@@ -1780,7 +1731,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1761,6 @@
           <t>3389211503</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
           <t>Tornitura, fresatura, rettifica conto terzi, oltre 20 anni. Via delle Cateratte 124.</t>
@@ -1818,7 +1768,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1848,7 +1798,6 @@
           <t>0575 966306</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
           <t>Tornitura e fresatura conto terzi, oltre 20 anni.</t>
@@ -1856,7 +1805,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1881,8 +1830,6 @@
           <t>Metalworking / Lavorazioni Metalliche</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
           <t>Meccanica di precisione, dal 1982, certificata ISO 9001:2008. Loc. Vallone 34/Q.</t>
@@ -1890,7 +1837,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1915,8 +1862,6 @@
           <t>Metalworking / Lavorazioni Metalliche</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
           <t>Tornitura, fresatura CNC, dal 1999.</t>
@@ -1924,7 +1869,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1949,8 +1894,6 @@
           <t>Metalworking / Lavorazioni Metalliche</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
           <t>Progettazione e assemblaggio strutture metalliche, dal 2001, oltre 25 anni esperienza.</t>
@@ -1958,7 +1901,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1988,7 +1931,6 @@
           <t>055 977571</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
           <t>Ferro battuto, rame, acciaio inox, dal 1982.</t>
@@ -1996,7 +1938,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -2006,7 +1948,6 @@
           <t>B.Mec di Burini Jacopo</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
           <t>Vacchereccia, Cavriglia (AR)</t>
@@ -2022,7 +1963,6 @@
           <t>055 9139232</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
           <t>Carpenteria/lavorazione ferro, produzione e manutenzione meccanica, dal 1980. Via Ferrino 3.</t>
@@ -2097,8 +2037,6 @@
           <t>Metalworking / Lavorazioni Metalliche</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
           <t>Carpenteria e lavorazione lamiera con taglio laser. Riclassificata da Siena a Firenze (provincia reale di Barberino Val d'Elsa).</t>
@@ -2136,7 +2074,6 @@
           <t>0577 305135</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
           <t>Lavorazione acciaio e acciaio inox, taglio laser conto terzi.</t>
@@ -2238,7 +2175,6 @@
           <t>Modulpanel Srl</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
           <t>Grosseto (GR)</t>
@@ -2254,7 +2190,6 @@
           <t>0564 1643161</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
           <t>Ragione sociale individuata tramite indirizzo (Via Repubblica Dominicana 33) e telefono. Carpenteria.</t>
@@ -2292,7 +2227,6 @@
           <t>0564 1724749</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
           <t>Progettazione, realizzazione, installazione e trattamento prodotti in ferro/inox/cor-ten.</t>
@@ -2310,7 +2244,6 @@
           <t>Carpenteria Metallica Tafi</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
           <t>Massa Marittima (GR)</t>
@@ -2326,7 +2259,6 @@
           <t>0566 919009</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
           <t>Lavorazione ferro artigianale, 40 anni attività. Via dei Colatori 19.</t>
@@ -2344,7 +2276,6 @@
           <t>CM Carpenteria Metallica Snc (di Sebastiani P. Lorenzini V.)</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
           <t>Carrara (MS)</t>
@@ -2360,7 +2291,6 @@
           <t>0585 55567</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
           <t>Carpenteria metallica, produzione prodotti primaria trasformazione acciaio.</t>
@@ -2435,8 +2365,6 @@
           <t>Metalworking / Lavorazioni Metalliche</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
           <t>Commercio ingrosso/dettaglio prodotti siderurgici e derivati.</t>
@@ -2454,7 +2382,6 @@
           <t>Galilei Srl</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
           <t>Carrara (MS)</t>
@@ -2470,7 +2397,6 @@
           <t>0585 916660</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
           <t>Carpenteria metallica. Via Passo della Volpe 110.</t>
@@ -2488,7 +2414,6 @@
           <t>Metaltecnica di Tartaglia Giuseppe &amp; C. Snc</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
           <t>Carrara (MS)</t>
@@ -2504,7 +2429,6 @@
           <t>0585 856547</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
           <t>Prefabbricati metallici, carpenteria. Via Passo della Volpe 31.</t>
@@ -2542,7 +2466,6 @@
           <t>334 8768126</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
           <t>Lavorazione ferro/carpenteria artigianale. Sede legale in realtà a Massarosa (LU), showroom operativo a Carrara.</t>
@@ -2560,7 +2483,6 @@
           <t>Micam Sas di Lorenzo Arduini e C.</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
           <t>Massa (MS)</t>
@@ -2576,7 +2498,6 @@
           <t>0585 830056 / 0585 878916</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
           <t>Ragione sociale individuata tramite indirizzo (Via Vecchia Candia) e telefono. Carpenteria metallica.</t>
